--- a/Optimal_Driver_Allocation_Workbook.xlsx
+++ b/Optimal_Driver_Allocation_Workbook.xlsx
@@ -970,7 +970,7 @@
         <v>8.3348</v>
       </c>
       <c r="D2" s="1">
-        <v>0.106</v>
+        <v>0.122</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>17</v>
@@ -987,7 +987,7 @@
         <v>8.3348</v>
       </c>
       <c r="D3" s="1">
-        <v>0.02</v>
+        <v>0.023</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>17</v>
@@ -1004,7 +1004,7 @@
         <v>8.3348</v>
       </c>
       <c r="D4" s="1">
-        <v>57.59</v>
+        <v>72.858</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>17</v>
@@ -1021,7 +1021,7 @@
         <v>8.3348</v>
       </c>
       <c r="D5" s="1">
-        <v>11.322</v>
+        <v>10.721</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>17</v>
